--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB ANDRATX.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB ANDRATX.xlsx
@@ -565,13 +565,13 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>39.1708</v>
+        <v>34.6472</v>
       </c>
       <c r="E2" t="n">
-        <v>40.7066</v>
+        <v>38.7228</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5356</v>
+        <v>-4.0754</v>
       </c>
       <c r="G2" t="n">
         <v>18.1205</v>
@@ -610,13 +610,13 @@
         <v>26.5667</v>
       </c>
       <c r="S2" t="n">
-        <v>7.7999</v>
+        <v>3.2765</v>
       </c>
       <c r="T2" t="n">
-        <v>3.928</v>
+        <v>1.9443</v>
       </c>
       <c r="U2" t="n">
-        <v>3.8718</v>
+        <v>1.332</v>
       </c>
       <c r="V2" t="n">
         <v>16.9621</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. RAMIS NIELL</t>
+          <t>P. TABERNER PERALTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>3.087</v>
+        <v>1.878099999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4333</v>
+        <v>2.7935</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6536999999999999</v>
+        <v>-0.9153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1417</v>
+        <v>4.1099</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1011</v>
+        <v>1.318</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2428</v>
+        <v>2.7919</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3925</v>
+        <v>4.8933</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3658</v>
+        <v>2.6402</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0266</v>
+        <v>2.2533</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5342</v>
+        <v>-0.7833</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2648</v>
+        <v>-1.3221</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2694</v>
+        <v>0.5387</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7814</v>
+        <v>-0.1952999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.1487</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7814</v>
+        <v>1.9535</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8951</v>
+        <v>-0.2085</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8258</v>
+        <v>0.0491</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0693</v>
+        <v>-0.2573000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7312</v>
+        <v>-1.8279</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7312</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. TABERNER PERALTA</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>1.743799999999999</v>
+        <v>1.6008</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6319</v>
+        <v>19.343</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8881999999999999</v>
+        <v>-17.7426</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1099</v>
+        <v>22.4048</v>
       </c>
       <c r="H4" t="n">
-        <v>1.318</v>
+        <v>-1.4957</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7919</v>
+        <v>23.9012</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8933</v>
+        <v>60.8635</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6402</v>
+        <v>29.5251</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2533</v>
+        <v>31.3384</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7833</v>
+        <v>-38.4588</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3221</v>
+        <v>-31.0212</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5387</v>
+        <v>-7.4372</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1952999999999999</v>
+        <v>7.0323</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1487</v>
+        <v>-48.6402</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9535</v>
+        <v>55.6725</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3428</v>
+        <v>-12.0214</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1126</v>
+        <v>-3.5187</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2302000000000001</v>
+        <v>-8.5029</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8279</v>
+        <v>-15.8151</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>10.6384</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8279</v>
+        <v>-26.4538</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAGNE YADE</t>
+          <t>T. RAMIS NIELL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2044999999999999</v>
+        <v>1.2203</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0097</v>
+        <v>0.5121</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8050999999999999</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>1.228</v>
+        <v>0.1417</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5793</v>
+        <v>-0.1011</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3512</v>
+        <v>0.2428</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4366</v>
+        <v>-0.3925</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7859</v>
+        <v>-0.3658</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3493999999999999</v>
+        <v>-0.0266</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2084</v>
+        <v>0.5342</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2067</v>
+        <v>0.2648</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.001799999999999968</v>
+        <v>0.2694</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.3207</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5161</v>
+        <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0186</v>
+        <v>1.0284</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2065999999999999</v>
+        <v>0.9046</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2253</v>
+        <v>0.1238</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6093</v>
+        <v>-0.7312</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2771999999999999</v>
+        <v>-0.7312</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. VILLALON CAYETANO</t>
+          <t>A. DIAGNE YADE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5406</v>
+        <v>0.1441000000000003</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4771</v>
+        <v>-1.0097</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.06359999999999999</v>
+        <v>1.1539</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2726</v>
+        <v>1.228</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5827</v>
+        <v>1.5793</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3101</v>
+        <v>-0.3512</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0814</v>
+        <v>2.4366</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0409</v>
+        <v>2.7859</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>-0.3493999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3541</v>
+        <v>-1.2084</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6236999999999999</v>
+        <v>-1.2067</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2696</v>
+        <v>-0.001799999999999968</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1953</v>
+        <v>-3.3207</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>3.5161</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6587</v>
+        <v>-0.6700999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3631</v>
+        <v>0.2066</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2955</v>
+        <v>-0.8767</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2771999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. VICENS MOREY</t>
+          <t>C. VILLALON CAYETANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8016</v>
+        <v>-0.2424</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.395</v>
+        <v>-0.4771</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4066</v>
+        <v>0.2347</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.2397</v>
+        <v>-0.2726</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3651</v>
+        <v>-0.5827</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8746</v>
+        <v>0.3101</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9827</v>
+        <v>0.0814</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3224</v>
+        <v>0.0409</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6603</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2571</v>
+        <v>-0.3541</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0427</v>
+        <v>-0.6236999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2144</v>
+        <v>0.2696</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0457</v>
+        <v>-0.3604</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4153</v>
+        <v>-0.3631</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3696</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6559</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.9331</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. VASCENCO BADRAJAN</t>
+          <t>A. VICENS MOREY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9830000000000001</v>
+        <v>-1.3034</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1056</v>
+        <v>-0.5972</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8773999999999998</v>
+        <v>-0.7062</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9465999999999997</v>
+        <v>-3.2397</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4743000000000001</v>
+        <v>-1.3651</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4722999999999999</v>
+        <v>-1.8746</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4658</v>
+        <v>-0.9827</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3968</v>
+        <v>-0.3224</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06909999999999972</v>
+        <v>-0.6603</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5192</v>
+        <v>-2.2571</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9225</v>
+        <v>-1.0427</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4032000000000001</v>
+        <v>-1.2144</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5394</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3204</v>
+        <v>-0.5475</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0815</v>
+        <v>-0.6175</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4019</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>3.6559</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>3.9331</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4958</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>N. VASCENCO BADRAJAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1167</v>
+        <v>-1.3768</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.851700000000001</v>
+        <v>-0.3888999999999998</v>
       </c>
       <c r="F9" t="n">
-        <v>7.735100000000001</v>
+        <v>-0.9878</v>
       </c>
       <c r="G9" t="n">
-        <v>-9.378299999999999</v>
+        <v>0.9465999999999997</v>
       </c>
       <c r="H9" t="n">
-        <v>-21.4435</v>
+        <v>0.4743000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>12.0653</v>
+        <v>0.4722999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>14.4154</v>
+        <v>1.4658</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3156000000000003</v>
+        <v>1.3968</v>
       </c>
       <c r="L9" t="n">
-        <v>14.0998</v>
+        <v>0.06909999999999972</v>
       </c>
       <c r="M9" t="n">
-        <v>-23.7938</v>
+        <v>-0.5192</v>
       </c>
       <c r="N9" t="n">
-        <v>-21.759</v>
+        <v>-0.9225</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0348</v>
+        <v>0.4032000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>4.883599999999999</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-25.1991</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>30.0829</v>
+        <v>2.5394</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2825</v>
+        <v>-0.714</v>
       </c>
       <c r="T9" t="n">
-        <v>-6.0506</v>
+        <v>0.7981</v>
       </c>
       <c r="U9" t="n">
-        <v>8.3331</v>
+        <v>-1.5121</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09570000000000023</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>6.9824</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.8869</v>
+        <v>-1.4958</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>D. COOPER SPACIR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8032</v>
+        <v>-4.5648</v>
       </c>
       <c r="E10" t="n">
-        <v>8.0806</v>
+        <v>-3.0574</v>
       </c>
       <c r="F10" t="n">
-        <v>-11.8838</v>
+        <v>-1.5074</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08430000000000004</v>
+        <v>-2.7002</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.7031</v>
+        <v>-0.4876</v>
       </c>
       <c r="I10" t="n">
-        <v>7.7873</v>
+        <v>-2.2126</v>
       </c>
       <c r="J10" t="n">
-        <v>18.9301</v>
+        <v>0.2268</v>
       </c>
       <c r="K10" t="n">
-        <v>7.4941</v>
+        <v>0.1457999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>11.4359</v>
+        <v>0.081</v>
       </c>
       <c r="M10" t="n">
-        <v>-18.8459</v>
+        <v>-2.9269</v>
       </c>
       <c r="N10" t="n">
-        <v>-15.1972</v>
+        <v>-0.6334</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.6486</v>
+        <v>-2.2936</v>
       </c>
       <c r="P10" t="n">
-        <v>8.009</v>
+        <v>-1.5628</v>
       </c>
       <c r="Q10" t="n">
-        <v>-17.1902</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>25.1992</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3266</v>
+        <v>-0.3019</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5726</v>
+        <v>-0.3541</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.8993</v>
+        <v>0.0522</v>
       </c>
       <c r="V10" t="n">
-        <v>-9.57</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>4.7676</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.3376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. COOPER SPACIR</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.546799999999999</v>
+        <v>-4.6168</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5519</v>
+        <v>7.169</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9948</v>
+        <v>-11.7859</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7002</v>
+        <v>0.08430000000000004</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4876</v>
+        <v>-7.7031</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2126</v>
+        <v>7.7873</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2268</v>
+        <v>18.9301</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1457999999999999</v>
+        <v>7.4941</v>
       </c>
       <c r="L11" t="n">
-        <v>0.081</v>
+        <v>11.4359</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9269</v>
+        <v>-18.8459</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6334</v>
+        <v>-15.1972</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2936</v>
+        <v>-3.6486</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5628</v>
+        <v>8.009</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>-17.1902</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>25.1992</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2838</v>
+        <v>-3.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1515</v>
+        <v>0.6611999999999998</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4353</v>
+        <v>-3.8013</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-9.57</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>4.7676</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-14.3376</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BILBAO BORRAJO</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.277200000000001</v>
+        <v>-4.742100000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.452</v>
+        <v>-7.568199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8251</v>
+        <v>2.826099999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4758</v>
+        <v>-9.378299999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.516</v>
+        <v>-21.4435</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0403</v>
+        <v>12.0653</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9818</v>
+        <v>14.4154</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.0223</v>
+        <v>0.3156000000000003</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0405</v>
+        <v>14.0998</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.494</v>
+        <v>-23.7938</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4937</v>
+        <v>-21.759</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.000199999999999978</v>
+        <v>-2.0348</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7814</v>
+        <v>4.883599999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-25.1991</v>
       </c>
       <c r="R12" t="n">
-        <v>1.172</v>
+        <v>30.0829</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5261</v>
+        <v>-0.343</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1474</v>
+        <v>-3.7669</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6213</v>
+        <v>3.4238</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.5462</v>
+        <v>0.09570000000000023</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6642</v>
+        <v>6.9824</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.882</v>
+        <v>-6.8869</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.323899999999999</v>
+        <v>-5.280200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0446999999999993</v>
+        <v>-0.07699999999999974</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.3685</v>
+        <v>-5.203</v>
       </c>
       <c r="G13" t="n">
         <v>-5.0019</v>
@@ -1468,13 +1468,13 @@
         <v>8.985899999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1188</v>
+        <v>-1.0749</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0118</v>
+        <v>-1.1337</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1071</v>
+        <v>0.05839999999999996</v>
       </c>
       <c r="V13" t="n">
         <v>-2.3285</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>A. BILBAO BORRAJO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.6536</v>
+        <v>-6.693300000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>15.3217</v>
+        <v>-4.0587</v>
       </c>
       <c r="F14" t="n">
-        <v>-21.9751</v>
+        <v>-2.6345</v>
       </c>
       <c r="G14" t="n">
-        <v>22.4048</v>
+        <v>-2.4758</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4957</v>
+        <v>-2.516</v>
       </c>
       <c r="I14" t="n">
-        <v>23.9012</v>
+        <v>0.0403</v>
       </c>
       <c r="J14" t="n">
-        <v>60.8635</v>
+        <v>-1.9818</v>
       </c>
       <c r="K14" t="n">
-        <v>29.5251</v>
+        <v>-2.0223</v>
       </c>
       <c r="L14" t="n">
-        <v>31.3384</v>
+        <v>0.0405</v>
       </c>
       <c r="M14" t="n">
-        <v>-38.4588</v>
+        <v>-0.494</v>
       </c>
       <c r="N14" t="n">
-        <v>-31.0212</v>
+        <v>-0.4937</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.4372</v>
+        <v>-0.000199999999999978</v>
       </c>
       <c r="P14" t="n">
-        <v>7.0323</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q14" t="n">
-        <v>-48.6402</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>55.6725</v>
+        <v>1.172</v>
       </c>
       <c r="S14" t="n">
-        <v>-20.2754</v>
+        <v>0.1101</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.5405</v>
+        <v>0.5407</v>
       </c>
       <c r="U14" t="n">
-        <v>-12.7355</v>
+        <v>-0.4307</v>
       </c>
       <c r="V14" t="n">
-        <v>-15.8151</v>
+        <v>-3.5462</v>
       </c>
       <c r="W14" t="n">
-        <v>10.6384</v>
+        <v>-0.6642</v>
       </c>
       <c r="X14" t="n">
-        <v>-26.4538</v>
+        <v>-2.882</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>M. PERONA MARCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-14.0464</v>
+        <v>-12.0918</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.1304</v>
+        <v>-7.6351</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.9158</v>
+        <v>-4.4566</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.9201</v>
+        <v>-0.3180999999999998</v>
       </c>
       <c r="H15" t="n">
-        <v>-7.546</v>
+        <v>-0.06310000000000004</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.3738</v>
+        <v>-0.2549999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1901999999999999</v>
+        <v>3.385</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8313999999999999</v>
+        <v>4.1776</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.0216</v>
+        <v>-0.7925000000000004</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.729900000000001</v>
+        <v>-3.7031</v>
       </c>
       <c r="N15" t="n">
-        <v>-8.3775</v>
+        <v>-4.2407</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3524</v>
+        <v>0.5373999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7114</v>
+        <v>-6.055800000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-9.3765</v>
+        <v>-11.1345</v>
       </c>
       <c r="R15" t="n">
-        <v>13.088</v>
+        <v>5.079</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.1302</v>
+        <v>-4.8863</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9913000000000001</v>
+        <v>-1.1043</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.1216</v>
+        <v>-3.7822</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.7077</v>
+        <v>-0.8315999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4447</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>-5.1523</v>
+        <v>-2.0503</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PERONA MARCH</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>-14.0914</v>
+        <v>-12.8845</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.767200000000001</v>
+        <v>-8.1114</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.3242</v>
+        <v>-4.7733</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3180999999999998</v>
+        <v>-9.9201</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.06310000000000004</v>
+        <v>-7.546</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2549999999999999</v>
+        <v>-2.3738</v>
       </c>
       <c r="J16" t="n">
-        <v>3.385</v>
+        <v>-0.1901999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1776</v>
+        <v>0.8313999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7925000000000004</v>
+        <v>-1.0216</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.7031</v>
+        <v>-9.729900000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-4.2407</v>
+        <v>-8.3775</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5373999999999999</v>
+        <v>-1.3524</v>
       </c>
       <c r="P16" t="n">
-        <v>-6.055800000000001</v>
+        <v>3.7114</v>
       </c>
       <c r="Q16" t="n">
-        <v>-11.1345</v>
+        <v>-9.3765</v>
       </c>
       <c r="R16" t="n">
-        <v>5.079</v>
+        <v>13.088</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.885999999999999</v>
+        <v>-1.9687</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.2364</v>
+        <v>1.0107</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.6496</v>
+        <v>-2.9791</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8315999999999999</v>
+        <v>-4.7077</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>0.4447</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.0503</v>
+        <v>-5.1523</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>-14.4323</v>
+        <v>-12.9486</v>
       </c>
       <c r="E17" t="n">
-        <v>-11.6922</v>
+        <v>-11.2679</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.7401</v>
+        <v>-1.6807</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3399000000000003</v>
@@ -1780,13 +1780,13 @@
         <v>4.8835</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.0556</v>
+        <v>-1.5717</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2086999999999999</v>
+        <v>0.2157</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.847</v>
+        <v>-1.7874</v>
       </c>
       <c r="V17" t="n">
         <v>-4.1999</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>J. REDA COLL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>-26.1398</v>
+        <v>-29.8302</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.833500000000001</v>
+        <v>-16.6372</v>
       </c>
       <c r="F18" t="n">
-        <v>-21.3062</v>
+        <v>-13.1931</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.4155</v>
+        <v>-2.503499999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-8.664900000000001</v>
+        <v>-3.6328</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.750399999999999</v>
+        <v>1.1295</v>
       </c>
       <c r="J18" t="n">
-        <v>31.4948</v>
+        <v>13.6414</v>
       </c>
       <c r="K18" t="n">
-        <v>27.458</v>
+        <v>5.3569</v>
       </c>
       <c r="L18" t="n">
-        <v>4.0366</v>
+        <v>8.284599999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-44.9104</v>
+        <v>-16.1446</v>
       </c>
       <c r="N18" t="n">
-        <v>-36.1231</v>
+        <v>-8.9895</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.787099999999999</v>
+        <v>-7.1551</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7582</v>
+        <v>-8.399800000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-59.9701</v>
+        <v>-26.9572</v>
       </c>
       <c r="R18" t="n">
-        <v>58.2123</v>
+        <v>18.5577</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8223</v>
+        <v>-5.7213</v>
       </c>
       <c r="T18" t="n">
-        <v>5.466100000000001</v>
+        <v>-3.4888</v>
       </c>
       <c r="U18" t="n">
-        <v>-7.2885</v>
+        <v>-2.2326</v>
       </c>
       <c r="V18" t="n">
-        <v>-9.143699999999999</v>
+        <v>-13.2058</v>
       </c>
       <c r="W18" t="n">
-        <v>18.1755</v>
+        <v>0.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>-27.3196</v>
+        <v>-13.3732</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. REDA COLL</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-33.8096</v>
+        <v>-32.5929</v>
       </c>
       <c r="E19" t="n">
-        <v>-20.1547</v>
+        <v>-12.3805</v>
       </c>
       <c r="F19" t="n">
-        <v>-13.6548</v>
+        <v>-20.2125</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.503499999999999</v>
+        <v>-13.4155</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.6328</v>
+        <v>-8.664900000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1295</v>
+        <v>-4.750399999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>13.6414</v>
+        <v>31.4948</v>
       </c>
       <c r="K19" t="n">
-        <v>5.3569</v>
+        <v>27.458</v>
       </c>
       <c r="L19" t="n">
-        <v>8.284599999999999</v>
+        <v>4.0366</v>
       </c>
       <c r="M19" t="n">
-        <v>-16.1446</v>
+        <v>-44.9104</v>
       </c>
       <c r="N19" t="n">
-        <v>-8.9895</v>
+        <v>-36.1231</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.1551</v>
+        <v>-8.787099999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-8.399800000000001</v>
+        <v>-1.7582</v>
       </c>
       <c r="Q19" t="n">
-        <v>-26.9572</v>
+        <v>-59.9701</v>
       </c>
       <c r="R19" t="n">
-        <v>18.5577</v>
+        <v>58.2123</v>
       </c>
       <c r="S19" t="n">
-        <v>-9.7006</v>
+        <v>-8.275500000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-7.006600000000001</v>
+        <v>-2.0807</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.6945</v>
+        <v>-6.194599999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-13.2058</v>
+        <v>-9.143699999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1675</v>
+        <v>18.1755</v>
       </c>
       <c r="X19" t="n">
-        <v>-13.3732</v>
+        <v>-27.3196</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>-35.1847</v>
+        <v>-33.5721</v>
       </c>
       <c r="E20" t="n">
-        <v>-27.9952</v>
+        <v>-27.6314</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.189500000000001</v>
+        <v>-5.940900000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-18.3201</v>
@@ -2014,13 +2014,13 @@
         <v>13.6741</v>
       </c>
       <c r="S20" t="n">
-        <v>-5.1598</v>
+        <v>-3.547</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0968</v>
+        <v>-0.733</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.0629</v>
+        <v>-2.8142</v>
       </c>
       <c r="V20" t="n">
         <v>-10.3376</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>-38.3067</v>
+        <v>-34.4779</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.5878</v>
+        <v>-26.0071</v>
       </c>
       <c r="F21" t="n">
-        <v>-21.7191</v>
+        <v>-8.4709</v>
       </c>
       <c r="G21" t="n">
-        <v>-28.3121</v>
+        <v>-4.3489</v>
       </c>
       <c r="H21" t="n">
-        <v>-29.061</v>
+        <v>-0.7470999999999998</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7488000000000001</v>
+        <v>-3.6015</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.617699999999999</v>
+        <v>15.3582</v>
       </c>
       <c r="K21" t="n">
-        <v>-12.6908</v>
+        <v>13.1543</v>
       </c>
       <c r="L21" t="n">
-        <v>5.073</v>
+        <v>2.204</v>
       </c>
       <c r="M21" t="n">
-        <v>-20.6944</v>
+        <v>-19.7067</v>
       </c>
       <c r="N21" t="n">
-        <v>-16.3696</v>
+        <v>-13.9016</v>
       </c>
       <c r="O21" t="n">
-        <v>-4.3244</v>
+        <v>-5.8056</v>
       </c>
       <c r="P21" t="n">
-        <v>-5.2741</v>
+        <v>-26.3712</v>
       </c>
       <c r="Q21" t="n">
-        <v>-29.4967</v>
+        <v>-46.2962</v>
       </c>
       <c r="R21" t="n">
-        <v>24.2224</v>
+        <v>19.9251</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.9884</v>
+        <v>-2.8703</v>
       </c>
       <c r="T21" t="n">
-        <v>6.787100000000001</v>
+        <v>-0.7202000000000002</v>
       </c>
       <c r="U21" t="n">
-        <v>-9.775499999999999</v>
+        <v>-2.1502</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7316</v>
+        <v>-0.8876999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>13.7397</v>
+        <v>5.6511</v>
       </c>
       <c r="X21" t="n">
-        <v>-15.4716</v>
+        <v>-6.539</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>-40.0525</v>
+        <v>-35.3627</v>
       </c>
       <c r="E22" t="n">
-        <v>-22.6883</v>
+        <v>-21.6915</v>
       </c>
       <c r="F22" t="n">
-        <v>-17.364</v>
+        <v>-13.6713</v>
       </c>
       <c r="G22" t="n">
-        <v>-16.9155</v>
+        <v>-20.7053</v>
       </c>
       <c r="H22" t="n">
-        <v>-11.2528</v>
+        <v>-11.0464</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.6626</v>
+        <v>-9.659200000000002</v>
       </c>
       <c r="J22" t="n">
-        <v>0.123</v>
+        <v>8.1349</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1607</v>
+        <v>9.4217</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.0377</v>
+        <v>-1.2869</v>
       </c>
       <c r="M22" t="n">
-        <v>-17.0387</v>
+        <v>-28.8399</v>
       </c>
       <c r="N22" t="n">
-        <v>-15.4136</v>
+        <v>-20.4679</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6252</v>
+        <v>-8.372199999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.8137</v>
+        <v>-10.7437</v>
       </c>
       <c r="Q22" t="n">
-        <v>-26.5665</v>
+        <v>-38.6777</v>
       </c>
       <c r="R22" t="n">
-        <v>18.753</v>
+        <v>27.9341</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.593</v>
+        <v>-7.6267</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4002</v>
+        <v>-3.1731</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.1927</v>
+        <v>-4.453600000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-9.729900000000001</v>
+        <v>3.7131</v>
       </c>
       <c r="W22" t="n">
-        <v>4.1553</v>
+        <v>12.0247</v>
       </c>
       <c r="X22" t="n">
-        <v>-13.8856</v>
+        <v>-8.311399999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,76 +2200,76 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
-        <v>-40.1093</v>
+        <v>-40.0274</v>
       </c>
       <c r="E23" t="n">
-        <v>-23.5101</v>
+        <v>-22.8514</v>
       </c>
       <c r="F23" t="n">
-        <v>-16.5988</v>
+        <v>-17.1761</v>
       </c>
       <c r="G23" t="n">
-        <v>-20.7053</v>
+        <v>-16.9155</v>
       </c>
       <c r="H23" t="n">
-        <v>-11.0464</v>
+        <v>-11.2528</v>
       </c>
       <c r="I23" t="n">
-        <v>-9.659200000000002</v>
+        <v>-5.6626</v>
       </c>
       <c r="J23" t="n">
-        <v>8.1349</v>
+        <v>0.123</v>
       </c>
       <c r="K23" t="n">
-        <v>9.4217</v>
+        <v>4.1607</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2869</v>
+        <v>-4.0377</v>
       </c>
       <c r="M23" t="n">
-        <v>-28.8399</v>
+        <v>-17.0387</v>
       </c>
       <c r="N23" t="n">
-        <v>-20.4679</v>
+        <v>-15.4136</v>
       </c>
       <c r="O23" t="n">
-        <v>-8.372199999999999</v>
+        <v>-1.6252</v>
       </c>
       <c r="P23" t="n">
-        <v>-10.7437</v>
+        <v>-7.8137</v>
       </c>
       <c r="Q23" t="n">
-        <v>-38.6777</v>
+        <v>-26.5665</v>
       </c>
       <c r="R23" t="n">
-        <v>27.9341</v>
+        <v>18.753</v>
       </c>
       <c r="S23" t="n">
-        <v>-12.3731</v>
+        <v>-5.568</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.9916</v>
+        <v>-0.5634000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-7.3812</v>
+        <v>-5.0048</v>
       </c>
       <c r="V23" t="n">
-        <v>3.7131</v>
+        <v>-9.729900000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>12.0247</v>
+        <v>4.1553</v>
       </c>
       <c r="X23" t="n">
-        <v>-8.311399999999999</v>
+        <v>-13.8856</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2278,70 +2278,70 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>-40.2629</v>
+        <v>-40.2501</v>
       </c>
       <c r="E24" t="n">
-        <v>-30.1113</v>
+        <v>-20.9975</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.1516</v>
+        <v>-19.2526</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.3489</v>
+        <v>-28.3121</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7470999999999998</v>
+        <v>-29.061</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.6015</v>
+        <v>0.7488000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>15.3582</v>
+        <v>-7.617699999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>13.1543</v>
+        <v>-12.6908</v>
       </c>
       <c r="L24" t="n">
-        <v>2.204</v>
+        <v>5.073</v>
       </c>
       <c r="M24" t="n">
-        <v>-19.7067</v>
+        <v>-20.6944</v>
       </c>
       <c r="N24" t="n">
-        <v>-13.9016</v>
+        <v>-16.3696</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.8056</v>
+        <v>-4.3244</v>
       </c>
       <c r="P24" t="n">
-        <v>-26.3712</v>
+        <v>-5.2741</v>
       </c>
       <c r="Q24" t="n">
-        <v>-46.2962</v>
+        <v>-29.4967</v>
       </c>
       <c r="R24" t="n">
-        <v>19.9251</v>
+        <v>24.2224</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.6553</v>
+        <v>-4.9325</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.8247</v>
+        <v>2.377</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.8305</v>
+        <v>-7.3091</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8876999999999999</v>
+        <v>-1.7316</v>
       </c>
       <c r="W24" t="n">
-        <v>5.6511</v>
+        <v>13.7397</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.539</v>
+        <v>-15.4716</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>-59.6282</v>
+        <v>-46.4313</v>
       </c>
       <c r="E25" t="n">
-        <v>-52.8636</v>
+        <v>-42.3712</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.764600000000001</v>
+        <v>-4.0599</v>
       </c>
       <c r="G25" t="n">
         <v>5.713200000000001</v>
@@ -2404,13 +2404,13 @@
         <v>52.547</v>
       </c>
       <c r="S25" t="n">
-        <v>-26.3333</v>
+        <v>-13.1365</v>
       </c>
       <c r="T25" t="n">
-        <v>-20.5269</v>
+        <v>-10.0345</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.8064</v>
+        <v>-3.1018</v>
       </c>
       <c r="V25" t="n">
         <v>6.3116</v>
@@ -2437,13 +2437,13 @@
         <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>-344.3133</v>
+        <v>-319.7988</v>
       </c>
       <c r="E26" t="n">
-        <v>-175.9585</v>
+        <v>-166.276</v>
       </c>
       <c r="F26" t="n">
-        <v>-168.3535</v>
+        <v>-153.5231</v>
       </c>
       <c r="G26" t="n">
         <v>-85.41849999999999</v>
@@ -2452,7 +2452,7 @@
         <v>-123.2209</v>
       </c>
       <c r="I26" t="n">
-        <v>37.8047</v>
+        <v>37.80469999999999</v>
       </c>
       <c r="J26" t="n">
         <v>238.7044</v>
@@ -2479,16 +2479,16 @@
         <v>-516.6799999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>417.0572999999999</v>
+        <v>417.0573</v>
       </c>
       <c r="S26" t="n">
-        <v>-99.5848</v>
+        <v>-75.0712</v>
       </c>
       <c r="T26" t="n">
-        <v>-32.6279</v>
+        <v>-22.944</v>
       </c>
       <c r="U26" t="n">
-        <v>-66.958</v>
+        <v>-52.1277</v>
       </c>
       <c r="V26" t="n">
         <v>-59.68389999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB ANDRATX.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB ANDRATX.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. TABERNER PERALTA</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>1.878099999999999</v>
+        <v>6.098</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7935</v>
+        <v>6.098</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9153</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1099</v>
+        <v>6.098</v>
       </c>
       <c r="H3" t="n">
-        <v>1.318</v>
+        <v>2.456</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7919</v>
+        <v>3.642</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8933</v>
+        <v>6.098</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6402</v>
+        <v>2.456</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2533</v>
+        <v>3.642</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7833</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3221</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5387</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1952999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1487</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9535</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2085</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0491</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2573000000000001</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>P. TABERNER PERALTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6008</v>
+        <v>1.878099999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>19.343</v>
+        <v>2.7935</v>
       </c>
       <c r="F4" t="n">
-        <v>-17.7426</v>
+        <v>-0.9153</v>
       </c>
       <c r="G4" t="n">
-        <v>22.4048</v>
+        <v>4.1099</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4957</v>
+        <v>1.318</v>
       </c>
       <c r="I4" t="n">
-        <v>23.9012</v>
+        <v>2.7919</v>
       </c>
       <c r="J4" t="n">
-        <v>60.8635</v>
+        <v>4.8933</v>
       </c>
       <c r="K4" t="n">
-        <v>29.5251</v>
+        <v>2.6402</v>
       </c>
       <c r="L4" t="n">
-        <v>31.3384</v>
+        <v>2.2533</v>
       </c>
       <c r="M4" t="n">
-        <v>-38.4588</v>
+        <v>-0.7833</v>
       </c>
       <c r="N4" t="n">
-        <v>-31.0212</v>
+        <v>-1.3221</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.4372</v>
+        <v>0.5387</v>
       </c>
       <c r="P4" t="n">
-        <v>7.0323</v>
+        <v>-0.1952999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-48.6402</v>
+        <v>-2.1487</v>
       </c>
       <c r="R4" t="n">
-        <v>55.6725</v>
+        <v>1.9535</v>
       </c>
       <c r="S4" t="n">
-        <v>-12.0214</v>
+        <v>-0.2085</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.5187</v>
+        <v>0.0491</v>
       </c>
       <c r="U4" t="n">
-        <v>-8.5029</v>
+        <v>-0.2573000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-15.8151</v>
+        <v>-1.8279</v>
       </c>
       <c r="W4" t="n">
-        <v>10.6384</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-26.4538</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. RAMIS NIELL</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2203</v>
+        <v>1.6008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5121</v>
+        <v>19.343</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7082000000000001</v>
+        <v>-17.7426</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1417</v>
+        <v>22.4048</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1011</v>
+        <v>-1.4957</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2428</v>
+        <v>23.9012</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3925</v>
+        <v>60.8635</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3658</v>
+        <v>29.5251</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0266</v>
+        <v>31.3384</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5342</v>
+        <v>-38.4588</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2648</v>
+        <v>-31.0212</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2694</v>
+        <v>-7.4372</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7814</v>
+        <v>7.0323</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-48.6402</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>55.6725</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0284</v>
+        <v>-12.0214</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9046</v>
+        <v>-3.5187</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1238</v>
+        <v>-8.5029</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7312</v>
+        <v>-15.8151</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>10.6384</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7312</v>
+        <v>-26.4538</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DIAGNE YADE</t>
+          <t>T. RAMIS NIELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1441000000000003</v>
+        <v>1.2203</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0097</v>
+        <v>0.5121</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1539</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>1.228</v>
+        <v>0.1417</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5793</v>
+        <v>-0.1011</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3512</v>
+        <v>0.2428</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4366</v>
+        <v>-0.3925</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7859</v>
+        <v>-0.3658</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3493999999999999</v>
+        <v>-0.0266</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2084</v>
+        <v>0.5342</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2067</v>
+        <v>0.2648</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001799999999999968</v>
+        <v>0.2694</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.3207</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.5161</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6700999999999999</v>
+        <v>1.0284</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2066</v>
+        <v>0.9046</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8767</v>
+        <v>0.1238</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6093</v>
+        <v>-0.7312</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2771999999999999</v>
+        <v>-0.7312</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. VILLALON CAYETANO</t>
+          <t>A. DIAGNE YADE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2424</v>
+        <v>0.1441000000000003</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4771</v>
+        <v>-1.0097</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2347</v>
+        <v>1.1539</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2726</v>
+        <v>1.228</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5827</v>
+        <v>1.5793</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3101</v>
+        <v>-0.3512</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0814</v>
+        <v>2.4366</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0409</v>
+        <v>2.7859</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>-0.3493999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3541</v>
+        <v>-1.2084</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6236999999999999</v>
+        <v>-1.2067</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2696</v>
+        <v>-0.001799999999999968</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>-3.3207</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>3.5161</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3604</v>
+        <v>-0.6700999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3631</v>
+        <v>0.2066</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002700000000000001</v>
+        <v>-0.8767</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2771999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VICENS MOREY</t>
+          <t>C. VILLALON CAYETANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3034</v>
+        <v>-0.2424</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5972</v>
+        <v>-0.4771</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7062</v>
+        <v>0.2347</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.2397</v>
+        <v>-0.2726</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3651</v>
+        <v>-0.5827</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8746</v>
+        <v>0.3101</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9827</v>
+        <v>0.0814</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3224</v>
+        <v>0.0409</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6603</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2571</v>
+        <v>-0.3541</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0427</v>
+        <v>-0.6236999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2144</v>
+        <v>0.2696</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5475</v>
+        <v>-0.3604</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6175</v>
+        <v>-0.3631</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>3.6559</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.9331</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. VASCENCO BADRAJAN</t>
+          <t>A. VICENS MOREY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3768</v>
+        <v>-1.3034</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3888999999999998</v>
+        <v>-0.5972</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9878</v>
+        <v>-0.7062</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9465999999999997</v>
+        <v>-3.2397</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4743000000000001</v>
+        <v>-1.3651</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4722999999999999</v>
+        <v>-1.8746</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4658</v>
+        <v>-0.9827</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3968</v>
+        <v>-0.3224</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06909999999999972</v>
+        <v>-0.6603</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5192</v>
+        <v>-2.2571</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9225</v>
+        <v>-1.0427</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4032000000000001</v>
+        <v>-1.2144</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5394</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.714</v>
+        <v>-0.5475</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7981</v>
+        <v>-0.6175</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5121</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>3.6559</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>3.9331</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4958</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. COOPER SPACIR</t>
+          <t>N. VASCENCO BADRAJAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5648</v>
+        <v>-1.3768</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0574</v>
+        <v>-0.3888999999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5074</v>
+        <v>-0.9878</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7002</v>
+        <v>0.9465999999999997</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4876</v>
+        <v>0.4743000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2126</v>
+        <v>0.4722999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2268</v>
+        <v>1.4658</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1457999999999999</v>
+        <v>1.3968</v>
       </c>
       <c r="L10" t="n">
-        <v>0.081</v>
+        <v>0.06909999999999972</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9269</v>
+        <v>-0.5192</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6334</v>
+        <v>-0.9225</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.2936</v>
+        <v>0.4032000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5628</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>2.5394</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3019</v>
+        <v>-0.714</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3541</v>
+        <v>0.7981</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0522</v>
+        <v>-1.5121</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4958</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>D. COOPER SPACIR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6168</v>
+        <v>-4.5648</v>
       </c>
       <c r="E11" t="n">
-        <v>7.169</v>
+        <v>-3.0574</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.7859</v>
+        <v>-1.5074</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08430000000000004</v>
+        <v>-2.7002</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.7031</v>
+        <v>-0.4876</v>
       </c>
       <c r="I11" t="n">
-        <v>7.7873</v>
+        <v>-2.2126</v>
       </c>
       <c r="J11" t="n">
-        <v>18.9301</v>
+        <v>0.2268</v>
       </c>
       <c r="K11" t="n">
-        <v>7.4941</v>
+        <v>0.1457999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>11.4359</v>
+        <v>0.081</v>
       </c>
       <c r="M11" t="n">
-        <v>-18.8459</v>
+        <v>-2.9269</v>
       </c>
       <c r="N11" t="n">
-        <v>-15.1972</v>
+        <v>-0.6334</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.6486</v>
+        <v>-2.2936</v>
       </c>
       <c r="P11" t="n">
-        <v>8.009</v>
+        <v>-1.5628</v>
       </c>
       <c r="Q11" t="n">
-        <v>-17.1902</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>25.1992</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.14</v>
+        <v>-0.3019</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6611999999999998</v>
+        <v>-0.3541</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.8013</v>
+        <v>0.0522</v>
       </c>
       <c r="V11" t="n">
-        <v>-9.57</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>4.7676</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-14.3376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.742100000000002</v>
+        <v>-4.6168</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.568199999999999</v>
+        <v>7.169</v>
       </c>
       <c r="F12" t="n">
-        <v>2.826099999999999</v>
+        <v>-11.7859</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.378299999999999</v>
+        <v>0.08430000000000004</v>
       </c>
       <c r="H12" t="n">
-        <v>-21.4435</v>
+        <v>-7.7031</v>
       </c>
       <c r="I12" t="n">
-        <v>12.0653</v>
+        <v>7.7873</v>
       </c>
       <c r="J12" t="n">
-        <v>14.4154</v>
+        <v>18.9301</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3156000000000003</v>
+        <v>7.4941</v>
       </c>
       <c r="L12" t="n">
-        <v>14.0998</v>
+        <v>11.4359</v>
       </c>
       <c r="M12" t="n">
-        <v>-23.7938</v>
+        <v>-18.8459</v>
       </c>
       <c r="N12" t="n">
-        <v>-21.759</v>
+        <v>-15.1972</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.0348</v>
+        <v>-3.6486</v>
       </c>
       <c r="P12" t="n">
-        <v>4.883599999999999</v>
+        <v>8.009</v>
       </c>
       <c r="Q12" t="n">
-        <v>-25.1991</v>
+        <v>-17.1902</v>
       </c>
       <c r="R12" t="n">
-        <v>30.0829</v>
+        <v>25.1992</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.343</v>
+        <v>-3.14</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.7669</v>
+        <v>0.6611999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4238</v>
+        <v>-3.8013</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09570000000000023</v>
+        <v>-9.57</v>
       </c>
       <c r="W12" t="n">
-        <v>6.9824</v>
+        <v>4.7676</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.8869</v>
+        <v>-14.3376</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. PONS AVECILLAS</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.280200000000001</v>
+        <v>-4.742100000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.07699999999999974</v>
+        <v>-7.568199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.203</v>
+        <v>2.826099999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.0019</v>
+        <v>-9.378299999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.9779</v>
+        <v>-21.4435</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0238</v>
+        <v>12.0653</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8698</v>
+        <v>14.4154</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1378</v>
+        <v>0.3156000000000003</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7323999999999995</v>
+        <v>14.0998</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.8718</v>
+        <v>-23.7938</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.1155</v>
+        <v>-21.759</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7564</v>
+        <v>-2.0348</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1256</v>
+        <v>4.883599999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.8602</v>
+        <v>-25.1991</v>
       </c>
       <c r="R13" t="n">
-        <v>8.985899999999999</v>
+        <v>30.0829</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0749</v>
+        <v>-0.343</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1337</v>
+        <v>-3.7669</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05839999999999996</v>
+        <v>3.4238</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3285</v>
+        <v>0.09570000000000023</v>
       </c>
       <c r="W13" t="n">
-        <v>3.0465</v>
+        <v>6.9824</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.3752</v>
+        <v>-6.8869</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. BILBAO BORRAJO</t>
+          <t>S. PONS AVECILLAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.693300000000001</v>
+        <v>-5.280200000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.0587</v>
+        <v>-0.07699999999999974</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.6345</v>
+        <v>-5.203</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.4758</v>
+        <v>-5.0019</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.516</v>
+        <v>-3.9779</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0403</v>
+        <v>-1.0238</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.9818</v>
+        <v>3.8698</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.0223</v>
+        <v>3.1378</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0405</v>
+        <v>0.7323999999999995</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.494</v>
+        <v>-8.8718</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4937</v>
+        <v>-7.1155</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.000199999999999978</v>
+        <v>-1.7564</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7814</v>
+        <v>3.1256</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-5.8602</v>
       </c>
       <c r="R14" t="n">
-        <v>1.172</v>
+        <v>8.985899999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1101</v>
+        <v>-1.0749</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5407</v>
+        <v>-1.1337</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4307</v>
+        <v>0.05839999999999996</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.5462</v>
+        <v>-2.3285</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6642</v>
+        <v>3.0465</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.882</v>
+        <v>-5.3752</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PERONA MARCH</t>
+          <t>A. BILBAO BORRAJO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-12.0918</v>
+        <v>-6.693300000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.6351</v>
+        <v>-4.0587</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.4566</v>
+        <v>-2.6345</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3180999999999998</v>
+        <v>-2.4758</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06310000000000004</v>
+        <v>-2.516</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2549999999999999</v>
+        <v>0.0403</v>
       </c>
       <c r="J15" t="n">
-        <v>3.385</v>
+        <v>-1.9818</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1776</v>
+        <v>-2.0223</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7925000000000004</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.7031</v>
+        <v>-0.494</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.2407</v>
+        <v>-0.4937</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5373999999999999</v>
+        <v>-0.000199999999999978</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.055800000000001</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-11.1345</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>5.079</v>
+        <v>1.172</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.8863</v>
+        <v>0.1101</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1043</v>
+        <v>0.5407</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.7822</v>
+        <v>-0.4307</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8315999999999999</v>
+        <v>-3.5462</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.0503</v>
+        <v>-2.882</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>M. PERONA MARCH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-12.8845</v>
+        <v>-12.0918</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.1114</v>
+        <v>-7.6351</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.7733</v>
+        <v>-4.4566</v>
       </c>
       <c r="G16" t="n">
-        <v>-9.9201</v>
+        <v>-0.3180999999999998</v>
       </c>
       <c r="H16" t="n">
-        <v>-7.546</v>
+        <v>-0.06310000000000004</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.3738</v>
+        <v>-0.2549999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1901999999999999</v>
+        <v>3.385</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8313999999999999</v>
+        <v>4.1776</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.0216</v>
+        <v>-0.7925000000000004</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.729900000000001</v>
+        <v>-3.7031</v>
       </c>
       <c r="N16" t="n">
-        <v>-8.3775</v>
+        <v>-4.2407</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3524</v>
+        <v>0.5373999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>3.7114</v>
+        <v>-6.055800000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-9.3765</v>
+        <v>-11.1345</v>
       </c>
       <c r="R16" t="n">
-        <v>13.088</v>
+        <v>5.079</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9687</v>
+        <v>-4.8863</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0107</v>
+        <v>-1.1043</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.9791</v>
+        <v>-3.7822</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.7077</v>
+        <v>-0.8315999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4447</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.1523</v>
+        <v>-2.0503</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. HUGUET CARRASCO</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>-12.9486</v>
+        <v>-12.8845</v>
       </c>
       <c r="E17" t="n">
-        <v>-11.2679</v>
+        <v>-8.1114</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6807</v>
+        <v>-4.7733</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3399000000000003</v>
+        <v>-9.9201</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.267600000000001</v>
+        <v>-7.546</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9277</v>
+        <v>-2.3738</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2369999999999997</v>
+        <v>-0.1901999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3431</v>
+        <v>0.8313999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5801</v>
+        <v>-1.0216</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5768</v>
+        <v>-9.729900000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9245</v>
+        <v>-8.3775</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3477</v>
+        <v>-1.3524</v>
       </c>
       <c r="P17" t="n">
-        <v>-6.837</v>
+        <v>3.7114</v>
       </c>
       <c r="Q17" t="n">
-        <v>-11.7205</v>
+        <v>-9.3765</v>
       </c>
       <c r="R17" t="n">
-        <v>4.8835</v>
+        <v>13.088</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5717</v>
+        <v>-1.9687</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2157</v>
+        <v>1.0107</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.7874</v>
+        <v>-2.9791</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.1999</v>
+        <v>-4.7077</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.4447</v>
       </c>
       <c r="X17" t="n">
-        <v>-4.1999</v>
+        <v>-5.1523</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. REDA COLL</t>
+          <t>L. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>-29.8302</v>
+        <v>-12.9486</v>
       </c>
       <c r="E18" t="n">
-        <v>-16.6372</v>
+        <v>-11.2679</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.1931</v>
+        <v>-1.6807</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.503499999999999</v>
+        <v>-0.3399000000000003</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.6328</v>
+        <v>-3.267600000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1295</v>
+        <v>2.9277</v>
       </c>
       <c r="J18" t="n">
-        <v>13.6414</v>
+        <v>0.2369999999999997</v>
       </c>
       <c r="K18" t="n">
-        <v>5.3569</v>
+        <v>-1.3431</v>
       </c>
       <c r="L18" t="n">
-        <v>8.284599999999999</v>
+        <v>1.5801</v>
       </c>
       <c r="M18" t="n">
-        <v>-16.1446</v>
+        <v>-0.5768</v>
       </c>
       <c r="N18" t="n">
-        <v>-8.9895</v>
+        <v>-1.9245</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.1551</v>
+        <v>1.3477</v>
       </c>
       <c r="P18" t="n">
-        <v>-8.399800000000001</v>
+        <v>-6.837</v>
       </c>
       <c r="Q18" t="n">
-        <v>-26.9572</v>
+        <v>-11.7205</v>
       </c>
       <c r="R18" t="n">
-        <v>18.5577</v>
+        <v>4.8835</v>
       </c>
       <c r="S18" t="n">
-        <v>-5.7213</v>
+        <v>-1.5717</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.4888</v>
+        <v>0.2157</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.2326</v>
+        <v>-1.7874</v>
       </c>
       <c r="V18" t="n">
-        <v>-13.2058</v>
+        <v>-4.1999</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-13.3732</v>
+        <v>-4.1999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>J. REDA COLL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>-32.5929</v>
+        <v>-29.8302</v>
       </c>
       <c r="E19" t="n">
-        <v>-12.3805</v>
+        <v>-16.6372</v>
       </c>
       <c r="F19" t="n">
-        <v>-20.2125</v>
+        <v>-13.1931</v>
       </c>
       <c r="G19" t="n">
-        <v>-13.4155</v>
+        <v>-2.503499999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.664900000000001</v>
+        <v>-3.6328</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.750399999999999</v>
+        <v>1.1295</v>
       </c>
       <c r="J19" t="n">
-        <v>31.4948</v>
+        <v>13.6414</v>
       </c>
       <c r="K19" t="n">
-        <v>27.458</v>
+        <v>5.3569</v>
       </c>
       <c r="L19" t="n">
-        <v>4.0366</v>
+        <v>8.284599999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-44.9104</v>
+        <v>-16.1446</v>
       </c>
       <c r="N19" t="n">
-        <v>-36.1231</v>
+        <v>-8.9895</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.787099999999999</v>
+        <v>-7.1551</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7582</v>
+        <v>-8.399800000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-59.9701</v>
+        <v>-26.9572</v>
       </c>
       <c r="R19" t="n">
-        <v>58.2123</v>
+        <v>18.5577</v>
       </c>
       <c r="S19" t="n">
-        <v>-8.275500000000001</v>
+        <v>-5.7213</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.0807</v>
+        <v>-3.4888</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.194599999999999</v>
+        <v>-2.2326</v>
       </c>
       <c r="V19" t="n">
-        <v>-9.143699999999999</v>
+        <v>-13.2058</v>
       </c>
       <c r="W19" t="n">
-        <v>18.1755</v>
+        <v>0.1675</v>
       </c>
       <c r="X19" t="n">
-        <v>-27.3196</v>
+        <v>-13.3732</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-33.5721</v>
+        <v>-32.5929</v>
       </c>
       <c r="E20" t="n">
-        <v>-27.6314</v>
+        <v>-12.3805</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.940900000000001</v>
+        <v>-20.2125</v>
       </c>
       <c r="G20" t="n">
-        <v>-18.3201</v>
+        <v>-13.4155</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.6307</v>
+        <v>-8.664900000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-6.6892</v>
+        <v>-4.750399999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.8644</v>
+        <v>31.4948</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.8304</v>
+        <v>27.458</v>
       </c>
       <c r="L20" t="n">
-        <v>-8.0336</v>
+        <v>4.0366</v>
       </c>
       <c r="M20" t="n">
-        <v>-8.455500000000001</v>
+        <v>-44.9104</v>
       </c>
       <c r="N20" t="n">
-        <v>-9.8005</v>
+        <v>-36.1231</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3448</v>
+        <v>-8.787099999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3673</v>
+        <v>-1.7582</v>
       </c>
       <c r="Q20" t="n">
-        <v>-15.0412</v>
+        <v>-59.9701</v>
       </c>
       <c r="R20" t="n">
-        <v>13.6741</v>
+        <v>58.2123</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.547</v>
+        <v>-8.275500000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.733</v>
+        <v>-2.0807</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.8142</v>
+        <v>-6.194599999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-10.3376</v>
+        <v>-9.143699999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.9926</v>
+        <v>18.1755</v>
       </c>
       <c r="X20" t="n">
-        <v>-8.345000000000001</v>
+        <v>-27.3196</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D21" t="n">
-        <v>-34.4779</v>
+        <v>-33.5721</v>
       </c>
       <c r="E21" t="n">
-        <v>-26.0071</v>
+        <v>-27.6314</v>
       </c>
       <c r="F21" t="n">
-        <v>-8.4709</v>
+        <v>-5.940900000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.3489</v>
+        <v>-18.3201</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7470999999999998</v>
+        <v>-11.6307</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6015</v>
+        <v>-6.6892</v>
       </c>
       <c r="J21" t="n">
-        <v>15.3582</v>
+        <v>-9.8644</v>
       </c>
       <c r="K21" t="n">
-        <v>13.1543</v>
+        <v>-1.8304</v>
       </c>
       <c r="L21" t="n">
-        <v>2.204</v>
+        <v>-8.0336</v>
       </c>
       <c r="M21" t="n">
-        <v>-19.7067</v>
+        <v>-8.455500000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-13.9016</v>
+        <v>-9.8005</v>
       </c>
       <c r="O21" t="n">
-        <v>-5.8056</v>
+        <v>1.3448</v>
       </c>
       <c r="P21" t="n">
-        <v>-26.3712</v>
+        <v>-1.3673</v>
       </c>
       <c r="Q21" t="n">
-        <v>-46.2962</v>
+        <v>-15.0412</v>
       </c>
       <c r="R21" t="n">
-        <v>19.9251</v>
+        <v>13.6741</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.8703</v>
+        <v>-3.547</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7202000000000002</v>
+        <v>-0.733</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.1502</v>
+        <v>-2.8142</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8876999999999999</v>
+        <v>-10.3376</v>
       </c>
       <c r="W21" t="n">
-        <v>5.6511</v>
+        <v>-1.9926</v>
       </c>
       <c r="X21" t="n">
-        <v>-6.539</v>
+        <v>-8.345000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>-35.3627</v>
+        <v>-34.4779</v>
       </c>
       <c r="E22" t="n">
-        <v>-21.6915</v>
+        <v>-26.0071</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.6713</v>
+        <v>-8.4709</v>
       </c>
       <c r="G22" t="n">
-        <v>-20.7053</v>
+        <v>-4.3489</v>
       </c>
       <c r="H22" t="n">
-        <v>-11.0464</v>
+        <v>-0.7470999999999998</v>
       </c>
       <c r="I22" t="n">
-        <v>-9.659200000000002</v>
+        <v>-3.6015</v>
       </c>
       <c r="J22" t="n">
-        <v>8.1349</v>
+        <v>15.3582</v>
       </c>
       <c r="K22" t="n">
-        <v>9.4217</v>
+        <v>13.1543</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2869</v>
+        <v>2.204</v>
       </c>
       <c r="M22" t="n">
-        <v>-28.8399</v>
+        <v>-19.7067</v>
       </c>
       <c r="N22" t="n">
-        <v>-20.4679</v>
+        <v>-13.9016</v>
       </c>
       <c r="O22" t="n">
-        <v>-8.372199999999999</v>
+        <v>-5.8056</v>
       </c>
       <c r="P22" t="n">
-        <v>-10.7437</v>
+        <v>-26.3712</v>
       </c>
       <c r="Q22" t="n">
-        <v>-38.6777</v>
+        <v>-46.2962</v>
       </c>
       <c r="R22" t="n">
-        <v>27.9341</v>
+        <v>19.9251</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.6267</v>
+        <v>-2.8703</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.1731</v>
+        <v>-0.7202000000000002</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.453600000000001</v>
+        <v>-2.1502</v>
       </c>
       <c r="V22" t="n">
-        <v>3.7131</v>
+        <v>-0.8876999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>12.0247</v>
+        <v>5.6511</v>
       </c>
       <c r="X22" t="n">
-        <v>-8.311399999999999</v>
+        <v>-6.539</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,70 +2200,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>-40.0274</v>
+        <v>-35.3627</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.8514</v>
+        <v>-21.6915</v>
       </c>
       <c r="F23" t="n">
-        <v>-17.1761</v>
+        <v>-13.6713</v>
       </c>
       <c r="G23" t="n">
-        <v>-16.9155</v>
+        <v>-20.7053</v>
       </c>
       <c r="H23" t="n">
-        <v>-11.2528</v>
+        <v>-11.0464</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.6626</v>
+        <v>-9.659200000000002</v>
       </c>
       <c r="J23" t="n">
-        <v>0.123</v>
+        <v>8.1349</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1607</v>
+        <v>9.4217</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.0377</v>
+        <v>-1.2869</v>
       </c>
       <c r="M23" t="n">
-        <v>-17.0387</v>
+        <v>-28.8399</v>
       </c>
       <c r="N23" t="n">
-        <v>-15.4136</v>
+        <v>-20.4679</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6252</v>
+        <v>-8.372199999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.8137</v>
+        <v>-10.7437</v>
       </c>
       <c r="Q23" t="n">
-        <v>-26.5665</v>
+        <v>-38.6777</v>
       </c>
       <c r="R23" t="n">
-        <v>18.753</v>
+        <v>27.9341</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.568</v>
+        <v>-7.6267</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5634000000000001</v>
+        <v>-3.1731</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.0048</v>
+        <v>-4.453600000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-9.729900000000001</v>
+        <v>3.7131</v>
       </c>
       <c r="W23" t="n">
-        <v>4.1553</v>
+        <v>12.0247</v>
       </c>
       <c r="X23" t="n">
-        <v>-13.8856</v>
+        <v>-8.311399999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2356,147 +2356,225 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>-46.4313</v>
+        <v>-46.1254</v>
       </c>
       <c r="E25" t="n">
-        <v>-42.3712</v>
+        <v>-28.9493</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.0599</v>
+        <v>-17.1761</v>
       </c>
       <c r="G25" t="n">
-        <v>5.713200000000001</v>
+        <v>-23.0135</v>
       </c>
       <c r="H25" t="n">
-        <v>-20.3608</v>
+        <v>-13.7087</v>
       </c>
       <c r="I25" t="n">
-        <v>26.0742</v>
+        <v>-9.304599999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>49.0208</v>
+        <v>-5.974600000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>13.7561</v>
+        <v>1.7047</v>
       </c>
       <c r="L25" t="n">
-        <v>35.2644</v>
+        <v>-7.6797</v>
       </c>
       <c r="M25" t="n">
-        <v>-43.3073</v>
+        <v>-17.0387</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.1174</v>
+        <v>-15.4136</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.19</v>
+        <v>-1.6252</v>
       </c>
       <c r="P25" t="n">
-        <v>-45.3198</v>
+        <v>-7.8137</v>
       </c>
       <c r="Q25" t="n">
-        <v>-97.86669999999999</v>
+        <v>-26.5665</v>
       </c>
       <c r="R25" t="n">
-        <v>52.547</v>
+        <v>18.753</v>
       </c>
       <c r="S25" t="n">
-        <v>-13.1365</v>
+        <v>-5.568</v>
       </c>
       <c r="T25" t="n">
-        <v>-10.0345</v>
+        <v>-0.5634000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.1018</v>
+        <v>-5.0048</v>
       </c>
       <c r="V25" t="n">
-        <v>6.3116</v>
+        <v>-9.729900000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>16.5093</v>
+        <v>4.1553</v>
       </c>
       <c r="X25" t="n">
-        <v>-10.1979</v>
+        <v>-13.8856</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>E. ZUSTOVICH</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>22</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-46.4313</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-42.3712</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-4.0599</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.713200000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-20.3608</v>
+      </c>
+      <c r="I26" t="n">
+        <v>26.0742</v>
+      </c>
+      <c r="J26" t="n">
+        <v>49.0208</v>
+      </c>
+      <c r="K26" t="n">
+        <v>13.7561</v>
+      </c>
+      <c r="L26" t="n">
+        <v>35.2644</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-43.3073</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-34.1174</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-9.19</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-45.3198</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-97.86669999999999</v>
+      </c>
+      <c r="R26" t="n">
+        <v>52.547</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-13.1365</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-10.0345</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-3.1018</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.3116</v>
+      </c>
+      <c r="W26" t="n">
+        <v>16.5093</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-10.1979</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>CB ANDRATX</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D27" t="n">
         <v>-319.7988</v>
       </c>
-      <c r="E26" t="n">
-        <v>-166.276</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="E27" t="n">
+        <v>-166.2759</v>
+      </c>
+      <c r="F27" t="n">
         <v>-153.5231</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G27" t="n">
         <v>-85.41849999999999</v>
       </c>
-      <c r="H26" t="n">
-        <v>-123.2209</v>
-      </c>
-      <c r="I26" t="n">
-        <v>37.80469999999999</v>
-      </c>
-      <c r="J26" t="n">
-        <v>238.7044</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="H27" t="n">
+        <v>-123.2208</v>
+      </c>
+      <c r="I27" t="n">
+        <v>37.8047</v>
+      </c>
+      <c r="J27" t="n">
+        <v>238.7048</v>
+      </c>
+      <c r="K27" t="n">
         <v>138.0414</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>100.6636</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>-324.1219</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>-261.2628</v>
       </c>
-      <c r="O26" t="n">
-        <v>-62.8596</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="O27" t="n">
+        <v>-62.85959999999999</v>
+      </c>
+      <c r="P27" t="n">
         <v>-99.62520000000001</v>
       </c>
-      <c r="Q26" t="n">
-        <v>-516.6799999999999</v>
-      </c>
-      <c r="R26" t="n">
-        <v>417.0573</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="Q27" t="n">
+        <v>-516.6800000000001</v>
+      </c>
+      <c r="R27" t="n">
+        <v>417.0573000000001</v>
+      </c>
+      <c r="S27" t="n">
         <v>-75.0712</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>-22.944</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>-52.1277</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V27" t="n">
         <v>-59.68389999999999</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W27" t="n">
         <v>134.6431</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X27" t="n">
         <v>-194.3291</v>
       </c>
     </row>
